--- a/Decks/Sisay.xlsx
+++ b/Decks/Sisay.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FCDAC1-F07B-4254-A698-D9A93AAF6797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1985D0-F192-445E-8271-3A8941841283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5B09AAE-7FA7-4E16-A1BB-671F612E704D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5B09AAE-7FA7-4E16-A1BB-671F612E704D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sisay" sheetId="1" r:id="rId1"/>
@@ -835,10 +835,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="D85" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">

--- a/Decks/Sisay.xlsx
+++ b/Decks/Sisay.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1985D0-F192-445E-8271-3A8941841283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B98713-FCA5-4EB2-89FB-50FB16DE83F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5B09AAE-7FA7-4E16-A1BB-671F612E704D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5B09AAE-7FA7-4E16-A1BB-671F612E704D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sisay" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
   <si>
     <t>Função</t>
   </si>
@@ -194,9 +194,6 @@
     <t>Draw PW</t>
   </si>
   <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
     <t>Lolth, Spider Queen</t>
   </si>
   <si>
@@ -335,18 +332,12 @@
     <t>Sisay, Weatherlight Captain</t>
   </si>
   <si>
-    <t>Rings of Brighthearth</t>
-  </si>
-  <si>
     <t>Flux Channeler</t>
   </si>
   <si>
     <t>Ripples of Potential</t>
   </si>
   <si>
-    <t>Urza Assembles the Titans</t>
-  </si>
-  <si>
     <t>The Peregrine Dynamo</t>
   </si>
   <si>
@@ -393,6 +384,9 @@
   </si>
   <si>
     <t>Dismember</t>
+  </si>
+  <si>
+    <t>Fatespinner</t>
   </si>
 </sst>
 </file>
@@ -835,10 +829,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1375,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1555,10 +1549,10 @@
         <v>1</v>
       </c>
       <c r="C50" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
         <v>52</v>
-      </c>
-      <c r="D50" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1570,10 +1564,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1585,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1600,10 +1594,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1615,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1630,10 +1624,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" t="s">
         <v>58</v>
-      </c>
-      <c r="D55" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1645,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,10 +1654,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1675,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1690,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1705,10 +1699,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1720,360 +1714,360 @@
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D62" t="s">
         <v>66</v>
-      </c>
-      <c r="B62" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D62" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C63" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" t="s">
         <v>68</v>
-      </c>
-      <c r="D63" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C72" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72" t="s">
         <v>79</v>
-      </c>
-      <c r="D72" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C73" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" t="s">
         <v>81</v>
-      </c>
-      <c r="D73" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C74" s="6" t="s">
+      <c r="D74" t="s">
         <v>84</v>
-      </c>
-      <c r="D74" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D76" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D77" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D78" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D79" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D80" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>92</v>
+      </c>
+      <c r="B82" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B82" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="D82" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B84" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>97</v>
-      </c>
       <c r="D84" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2088,14 +2082,14 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D86" t="s">
         <v>99</v>
@@ -2103,227 +2097,227 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D87" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D88" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D89" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D90" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D91" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D92" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D94" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D95" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D96" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D97" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D98" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D99" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D100" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
